--- a/AAAGameData/DataTables/PlayerAccountTable.xlsx
+++ b/AAAGameData/DataTables/PlayerAccountTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Statistics</t>
   </si>
   <si>
-    <t>PlayerPos</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>Vector3</t>
-  </si>
-  <si>
     <t>玩家ID</t>
   </si>
   <si>
@@ -201,9 +195,6 @@
   </si>
   <si>
     <t>统计数据</t>
-  </si>
-  <si>
-    <t>玩家坐标</t>
   </si>
 </sst>
 </file>
@@ -216,14 +207,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -679,148 +663,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1178,8 +1162,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1206,10 +1190,9 @@
     <col min="24" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="10" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,9 +1223,8 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,172 +1301,163 @@
       <c r="Z2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:26">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="O3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="S3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="U3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:26">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="N4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="U4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="V4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="W4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="X4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
